--- a/public/tableView.xlsx
+++ b/public/tableView.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:H4"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -415,55 +415,55 @@
     <col min="8" max="8" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H2" t="s">
         <v>15</v>
       </c>
     </row>
